--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU01/HRM/post DDV_HRM-2031-0340/panel_11/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU01/HRM/post DDV_HRM-2031-0340/panel_11/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Back_Summary.xlsx
@@ -437,16 +437,6 @@
           <t>Radius</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -460,22 +450,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.6921</v>
+        <v>16.75022</v>
       </c>
       <c r="D2" t="n">
-        <v>16.62346</v>
+        <v>16.36914</v>
       </c>
       <c r="E2" t="n">
-        <v>16.637</v>
+        <v>16.51634</v>
       </c>
       <c r="F2" t="n">
-        <v>43.07288</v>
+        <v>42.23936</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05127</v>
+        <v>0.05089</v>
       </c>
       <c r="H2" t="n">
-        <v>1.83064</v>
+        <v>1.81805</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +475,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.61599</v>
+        <v>16.68955</v>
       </c>
       <c r="D3" t="n">
-        <v>16.24259</v>
+        <v>16.24693</v>
       </c>
       <c r="E3" t="n">
-        <v>16.83336</v>
+        <v>16.55482</v>
       </c>
       <c r="F3" t="n">
-        <v>42.50211</v>
+        <v>40.95519</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05079</v>
+        <v>0.04971</v>
       </c>
       <c r="H3" t="n">
-        <v>1.79434</v>
+        <v>1.80861</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +500,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.51666</v>
+        <v>16.84449</v>
       </c>
       <c r="D4" t="n">
-        <v>16.68972</v>
+        <v>16.37835</v>
       </c>
       <c r="E4" t="n">
-        <v>16.74143</v>
+        <v>16.78198</v>
       </c>
       <c r="F4" t="n">
-        <v>42.75309</v>
+        <v>43.21385</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04936</v>
+        <v>0.04964</v>
       </c>
       <c r="H4" t="n">
-        <v>1.82</v>
+        <v>1.78549</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +525,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.49761</v>
+        <v>16.70601</v>
       </c>
       <c r="D5" t="n">
-        <v>16.80633</v>
+        <v>16.47963</v>
       </c>
       <c r="E5" t="n">
-        <v>16.742</v>
+        <v>16.64161</v>
       </c>
       <c r="F5" t="n">
-        <v>42.59286</v>
+        <v>42.15017</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04984</v>
+        <v>0.04983</v>
       </c>
       <c r="H5" t="n">
-        <v>1.81031</v>
+        <v>1.82374</v>
       </c>
     </row>
     <row r="6">
@@ -559,10 +549,23 @@
           <t>Unit 5</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>scratched - not measurable</t>
-        </is>
+      <c r="C6" t="n">
+        <v>16.67825</v>
+      </c>
+      <c r="D6" t="n">
+        <v>16.16756</v>
+      </c>
+      <c r="E6" t="n">
+        <v>16.4197</v>
+      </c>
+      <c r="F6" t="n">
+        <v>41.74736</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.05092</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.77069</v>
       </c>
     </row>
     <row r="7">
@@ -572,22 +575,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.63016</v>
+        <v>16.87685</v>
       </c>
       <c r="D7" t="n">
-        <v>16.4079</v>
+        <v>16.1113</v>
       </c>
       <c r="E7" t="n">
-        <v>16.56824</v>
+        <v>16.73623</v>
       </c>
       <c r="F7" t="n">
-        <v>42.44955</v>
+        <v>42.03419</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05053</v>
+        <v>0.0503</v>
       </c>
       <c r="H7" t="n">
-        <v>1.81864</v>
+        <v>1.83745</v>
       </c>
     </row>
     <row r="8">
@@ -597,22 +600,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.86711</v>
+        <v>16.80727</v>
       </c>
       <c r="D8" t="n">
-        <v>16.6252</v>
+        <v>16.2003</v>
       </c>
       <c r="E8" t="n">
-        <v>16.58667</v>
+        <v>16.36071</v>
       </c>
       <c r="F8" t="n">
-        <v>42.21649</v>
+        <v>42.49618</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05116</v>
+        <v>0.05008</v>
       </c>
       <c r="H8" t="n">
-        <v>1.80461</v>
+        <v>1.78493</v>
       </c>
     </row>
     <row r="9">
@@ -622,22 +625,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.63934</v>
+        <v>16.95261</v>
       </c>
       <c r="D9" t="n">
-        <v>16.49192</v>
+        <v>15.96485</v>
       </c>
       <c r="E9" t="n">
-        <v>16.32892</v>
+        <v>16.65767</v>
       </c>
       <c r="F9" t="n">
-        <v>43.19519</v>
+        <v>41.97434</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05001</v>
+        <v>0.05083</v>
       </c>
       <c r="H9" t="n">
-        <v>1.82445</v>
+        <v>1.80177</v>
       </c>
     </row>
     <row r="10">
@@ -647,48 +650,33 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.03231</v>
+        <v>17.07025</v>
       </c>
       <c r="D10" t="n">
-        <v>16.18582</v>
+        <v>16.45514</v>
       </c>
       <c r="E10" t="n">
-        <v>16.59547</v>
+        <v>16.58782</v>
       </c>
       <c r="F10" t="n">
-        <v>41.79384</v>
+        <v>42.90351</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05111</v>
+        <v>0.04971</v>
       </c>
       <c r="H10" t="n">
-        <v>1.82099</v>
+        <v>1.8245</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>Max Stepheight</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Width</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Space</t>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -700,23 +688,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Trace 1</t>
+          <t>via 1</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.51052</v>
+        <v>0.59072</v>
       </c>
       <c r="D12" t="n">
-        <v>16.02004</v>
-      </c>
-      <c r="E12" t="n">
-        <v>16.1851</v>
-      </c>
-      <c r="F12" t="n">
-        <v>21.96262</v>
-      </c>
-      <c r="G12" t="n">
-        <v>34.71733</v>
+        <v>1.09196</v>
       </c>
     </row>
     <row r="13">
@@ -726,19 +705,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.47155</v>
+        <v>0.60087</v>
       </c>
       <c r="D13" t="n">
-        <v>16.0007</v>
-      </c>
-      <c r="E13" t="n">
-        <v>16.18926</v>
-      </c>
-      <c r="F13" t="n">
-        <v>21.4546</v>
-      </c>
-      <c r="G13" t="n">
-        <v>34.23181</v>
+        <v>1.11638</v>
       </c>
     </row>
     <row r="14">
@@ -747,25 +717,11 @@
           <t>Unit 9</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>re-measured</t>
-        </is>
-      </c>
       <c r="C14" t="n">
-        <v>16.0955</v>
+        <v>0.60048</v>
       </c>
       <c r="D14" t="n">
-        <v>15.84684</v>
-      </c>
-      <c r="E14" t="n">
-        <v>16.18916</v>
-      </c>
-      <c r="F14" t="n">
-        <v>21.25089</v>
-      </c>
-      <c r="G14" t="n">
-        <v>34.34253</v>
+        <v>1.11563</v>
       </c>
     </row>
     <row r="15">
@@ -775,19 +731,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16.59257</v>
+        <v>0.5971</v>
       </c>
       <c r="D15" t="n">
-        <v>15.58179</v>
-      </c>
-      <c r="E15" t="n">
-        <v>16.58591</v>
-      </c>
-      <c r="F15" t="n">
-        <v>21.72046</v>
-      </c>
-      <c r="G15" t="n">
-        <v>33.60489</v>
+        <v>1.13169</v>
       </c>
     </row>
     <row r="16">
@@ -797,19 +744,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16.65204</v>
+        <v>0.60024</v>
       </c>
       <c r="D16" t="n">
-        <v>16.16569</v>
-      </c>
-      <c r="E16" t="n">
-        <v>16.49961</v>
-      </c>
-      <c r="F16" t="n">
-        <v>22.10897</v>
-      </c>
-      <c r="G16" t="n">
-        <v>33.75525</v>
+        <v>1.12038</v>
       </c>
     </row>
     <row r="17">
@@ -819,19 +757,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>16.67188</v>
+        <v>0.60419</v>
       </c>
       <c r="D17" t="n">
-        <v>15.80127</v>
-      </c>
-      <c r="E17" t="n">
-        <v>16.41448</v>
-      </c>
-      <c r="F17" t="n">
-        <v>21.56571</v>
-      </c>
-      <c r="G17" t="n">
-        <v>34.00134</v>
+        <v>1.0963</v>
       </c>
     </row>
     <row r="18">
@@ -841,19 +770,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.55302</v>
+        <v>0.60934</v>
       </c>
       <c r="D18" t="n">
-        <v>15.749</v>
-      </c>
-      <c r="E18" t="n">
-        <v>16.32903</v>
-      </c>
-      <c r="F18" t="n">
-        <v>21.70403</v>
-      </c>
-      <c r="G18" t="n">
-        <v>34.65188</v>
+        <v>1.093</v>
       </c>
     </row>
     <row r="19">
@@ -863,19 +783,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16.50644</v>
+        <v>0.61032</v>
       </c>
       <c r="D19" t="n">
-        <v>15.82189</v>
-      </c>
-      <c r="E19" t="n">
-        <v>16.63236</v>
-      </c>
-      <c r="F19" t="n">
-        <v>21.85815</v>
-      </c>
-      <c r="G19" t="n">
-        <v>34.50267</v>
+        <v>1.12493</v>
       </c>
     </row>
     <row r="20">
@@ -885,19 +796,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16.30399</v>
+        <v>0.60454</v>
       </c>
       <c r="D20" t="n">
-        <v>16.06757</v>
-      </c>
-      <c r="E20" t="n">
-        <v>16.11132</v>
-      </c>
-      <c r="F20" t="n">
-        <v>21.79669</v>
-      </c>
-      <c r="G20" t="n">
-        <v>34.42424</v>
+        <v>1.089</v>
       </c>
     </row>
   </sheetData>
